--- a/docs/ophir/ophir-maliyet-talebi.xlsx
+++ b/docs/ophir/ophir-maliyet-talebi.xlsx
@@ -725,7 +725,7 @@
         <v/>
       </c>
       <c r="S2" s="10" t="n">
-        <v>5.13</v>
+        <v>7.53</v>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="S3" s="10" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v/>
       </c>
       <c r="S4" s="10" t="n">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v/>
       </c>
       <c r="S5" s="10" t="n">
-        <v>3.96</v>
+        <v>4.79</v>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v/>
       </c>
       <c r="S6" s="10" t="n">
-        <v>3.96</v>
+        <v>4.79</v>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="S7" s="10" t="n">
-        <v>3.96</v>
+        <v>4.79</v>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v/>
       </c>
       <c r="S8" s="10" t="n">
-        <v>5.93</v>
+        <v>7.18</v>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v/>
       </c>
       <c r="S9" s="10" t="n">
-        <v>5.93</v>
+        <v>7.18</v>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v/>
       </c>
       <c r="S10" s="10" t="n">
-        <v>6.92</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v/>
       </c>
       <c r="S11" s="10" t="n">
-        <v>3.06</v>
+        <v>3.71</v>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v/>
       </c>
       <c r="S12" s="10" t="n">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v/>
       </c>
       <c r="S13" s="10" t="n">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="S14" s="10" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v/>
       </c>
       <c r="S15" s="10" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v/>
       </c>
       <c r="S16" s="10" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="S17" s="10" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v/>
       </c>
       <c r="S18" s="10" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v/>
       </c>
       <c r="S19" s="10" t="n">
-        <v>9.59</v>
+        <v>11.6</v>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v/>
       </c>
       <c r="S20" s="10" t="n">
-        <v>3.96</v>
+        <v>4.79</v>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="S21" s="10" t="n">
-        <v>2.57</v>
+        <v>3.11</v>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v/>
       </c>
       <c r="S22" s="10" t="n">
-        <v>3.8</v>
+        <v>4.59</v>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v/>
       </c>
       <c r="S23" s="10" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v/>
       </c>
       <c r="S24" s="10" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v/>
       </c>
       <c r="S25" s="10" t="n">
-        <v>7.07</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v/>
       </c>
       <c r="S26" s="10" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v/>
       </c>
       <c r="S27" s="10" t="n">
-        <v>4.4</v>
+        <v>5.32</v>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v/>
       </c>
       <c r="S28" s="10" t="n">
-        <v>2.54</v>
+        <v>2.87</v>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v/>
       </c>
       <c r="S29" s="10" t="n">
-        <v>9.25</v>
+        <v>11.19</v>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v/>
       </c>
       <c r="S30" s="10" t="n">
-        <v>2.77</v>
+        <v>3.35</v>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v/>
       </c>
       <c r="S31" s="10" t="n">
-        <v>6.28</v>
+        <v>7.6</v>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v/>
       </c>
       <c r="S32" s="10" t="n">
-        <v>6.13</v>
+        <v>7.42</v>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v/>
       </c>
       <c r="S33" s="10" t="n">
-        <v>2.94</v>
+        <v>3.49</v>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v/>
       </c>
       <c r="S34" s="10" t="n">
-        <v>4.86</v>
+        <v>6.94</v>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v/>
       </c>
       <c r="S35" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="S36" s="10" t="n">
-        <v>5.59</v>
+        <v>7.98</v>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v/>
       </c>
       <c r="S37" s="10" t="n">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v/>
       </c>
       <c r="S38" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v/>
       </c>
       <c r="S39" s="10" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v/>
       </c>
       <c r="S40" s="10" t="n">
-        <v>3.71</v>
+        <v>3.81</v>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v/>
       </c>
       <c r="S41" s="10" t="n">
-        <v>9.69</v>
+        <v>11.72</v>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v/>
       </c>
       <c r="S42" s="10" t="n">
-        <v>2.77</v>
+        <v>3.35</v>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="S43" s="10" t="n">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v/>
       </c>
       <c r="S44" s="10" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="S45" s="10" t="n">
-        <v>2.85</v>
+        <v>4.07</v>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v/>
       </c>
       <c r="S46" s="10" t="n">
-        <v>2.87</v>
+        <v>3.47</v>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v/>
       </c>
       <c r="S47" s="10" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v/>
       </c>
       <c r="S48" s="10" t="n">
-        <v>3.26</v>
+        <v>3.95</v>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v/>
       </c>
       <c r="S49" s="10" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="S50" s="10" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v/>
       </c>
       <c r="S51" s="10" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v/>
       </c>
       <c r="S52" s="10" t="n">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v/>
       </c>
       <c r="S53" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v/>
       </c>
       <c r="S54" s="10" t="n">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v/>
       </c>
       <c r="S55" s="10" t="n">
-        <v>4.38</v>
+        <v>4.77</v>
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v/>
       </c>
       <c r="S56" s="10" t="n">
-        <v>4.02</v>
+        <v>4.53</v>
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v/>
       </c>
       <c r="S57" s="10" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v/>
       </c>
       <c r="S58" s="10" t="n">
-        <v>3.06</v>
+        <v>3.71</v>
       </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v/>
       </c>
       <c r="S59" s="10" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v/>
       </c>
       <c r="S60" s="10" t="n">
-        <v>5.45</v>
+        <v>7.78</v>
       </c>
       <c r="T60" s="3" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v/>
       </c>
       <c r="S61" s="10" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="T61" s="3" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v/>
       </c>
       <c r="S62" s="10" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v/>
       </c>
       <c r="S63" s="10" t="n">
-        <v>5.03</v>
+        <v>7.18</v>
       </c>
       <c r="T63" s="3" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v/>
       </c>
       <c r="S64" s="10" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="T64" s="3" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v/>
       </c>
       <c r="S65" s="10" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="T65" s="3" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v/>
       </c>
       <c r="S66" s="10" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="T66" s="3" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v/>
       </c>
       <c r="S67" s="10" t="n">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="T67" s="3" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v/>
       </c>
       <c r="S68" s="10" t="n">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="T68" s="3" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v/>
       </c>
       <c r="S69" s="10" t="n">
-        <v>5.74</v>
+        <v>6.94</v>
       </c>
       <c r="T69" s="3" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v/>
       </c>
       <c r="S70" s="10" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="T70" s="3" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v/>
       </c>
       <c r="S71" s="10" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="T71" s="3" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v/>
       </c>
       <c r="S72" s="10" t="n">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="T72" s="3" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v/>
       </c>
       <c r="S73" s="10" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="T73" s="3" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v/>
       </c>
       <c r="S74" s="10" t="n">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="T74" s="3" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v/>
       </c>
       <c r="S75" s="10" t="n">
-        <v>9.4</v>
+        <v>11.37</v>
       </c>
       <c r="T75" s="3" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v/>
       </c>
       <c r="S76" s="10" t="n">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="T76" s="3" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v/>
       </c>
       <c r="S77" s="10" t="n">
-        <v>5.19</v>
+        <v>7.42</v>
       </c>
       <c r="T77" s="3" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v/>
       </c>
       <c r="S78" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T78" s="3" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v/>
       </c>
       <c r="S79" s="10" t="n">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="T79" s="3" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v/>
       </c>
       <c r="S80" s="10" t="n">
-        <v>4.2</v>
+        <v>6.09</v>
       </c>
       <c r="T80" s="3" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v/>
       </c>
       <c r="S81" s="10" t="n">
-        <v>5.93</v>
+        <v>7.18</v>
       </c>
       <c r="T81" s="3" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v/>
       </c>
       <c r="S82" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T82" s="3" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v/>
       </c>
       <c r="S83" s="10" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="T83" s="3" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v/>
       </c>
       <c r="S84" s="10" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="T84" s="3" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v/>
       </c>
       <c r="S85" s="10" t="n">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="T85" s="3" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v/>
       </c>
       <c r="S86" s="10" t="n">
-        <v>4.62</v>
+        <v>5.18</v>
       </c>
       <c r="T86" s="3" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v/>
       </c>
       <c r="S87" s="10" t="n">
-        <v>5.07</v>
+        <v>7.78</v>
       </c>
       <c r="T87" s="3" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v/>
       </c>
       <c r="S88" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T88" s="3" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v/>
       </c>
       <c r="S89" s="10" t="n">
-        <v>6.43</v>
+        <v>7.78</v>
       </c>
       <c r="T89" s="3" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v/>
       </c>
       <c r="S90" s="10" t="n">
-        <v>2.91</v>
+        <v>3.45</v>
       </c>
       <c r="T90" s="3" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v/>
       </c>
       <c r="S91" s="10" t="n">
-        <v>1.48</v>
+        <v>4.31</v>
       </c>
       <c r="T91" s="3" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v/>
       </c>
       <c r="S92" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T92" s="3" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v/>
       </c>
       <c r="S93" s="10" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="T93" s="3" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v/>
       </c>
       <c r="S94" s="10" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="T94" s="3" t="inlineStr">
         <is>

--- a/docs/ophir/ophir-maliyet-talebi.xlsx
+++ b/docs/ophir/ophir-maliyet-talebi.xlsx
@@ -725,7 +725,7 @@
         <v/>
       </c>
       <c r="S2" s="10" t="n">
-        <v>7.53</v>
+        <v>8.67</v>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v/>
       </c>
       <c r="S15" s="10" t="n">
-        <v>1.49</v>
+        <v>2.09</v>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v/>
       </c>
       <c r="S18" s="10" t="n">
-        <v>1.68</v>
+        <v>2.27</v>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v/>
       </c>
       <c r="S25" s="10" t="n">
-        <v>9.529999999999999</v>
+        <v>10.17</v>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v/>
       </c>
       <c r="S28" s="10" t="n">
-        <v>2.87</v>
+        <v>4.34</v>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v/>
       </c>
       <c r="S33" s="10" t="n">
-        <v>3.49</v>
+        <v>4.96</v>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="S36" s="10" t="n">
-        <v>7.98</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v/>
       </c>
       <c r="S40" s="10" t="n">
-        <v>3.81</v>
+        <v>5.38</v>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v/>
       </c>
       <c r="S52" s="10" t="n">
-        <v>3.9</v>
+        <v>5.68</v>
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v/>
       </c>
       <c r="S54" s="10" t="n">
-        <v>3.63</v>
+        <v>5.26</v>
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v/>
       </c>
       <c r="S55" s="10" t="n">
-        <v>4.77</v>
+        <v>6.28</v>
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v/>
       </c>
       <c r="S56" s="10" t="n">
-        <v>4.53</v>
+        <v>6.31</v>
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v/>
       </c>
       <c r="S62" s="10" t="n">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v/>
       </c>
       <c r="S65" s="10" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="T65" s="3" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v/>
       </c>
       <c r="S66" s="10" t="n">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="T66" s="3" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v/>
       </c>
       <c r="S68" s="10" t="n">
-        <v>2.41</v>
+        <v>4.19</v>
       </c>
       <c r="T68" s="3" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v/>
       </c>
       <c r="S72" s="10" t="n">
-        <v>2.88</v>
+        <v>4.31</v>
       </c>
       <c r="T72" s="3" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v/>
       </c>
       <c r="S73" s="10" t="n">
-        <v>2.36</v>
+        <v>3.29</v>
       </c>
       <c r="T73" s="3" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v/>
       </c>
       <c r="S80" s="10" t="n">
-        <v>6.09</v>
+        <v>7.54</v>
       </c>
       <c r="T80" s="3" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v/>
       </c>
       <c r="S84" s="10" t="n">
-        <v>1.94</v>
+        <v>3.05</v>
       </c>
       <c r="T84" s="3" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v/>
       </c>
       <c r="S85" s="10" t="n">
-        <v>2.41</v>
+        <v>4.19</v>
       </c>
       <c r="T85" s="3" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v/>
       </c>
       <c r="S86" s="10" t="n">
-        <v>5.18</v>
+        <v>6.7</v>
       </c>
       <c r="T86" s="3" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v/>
       </c>
       <c r="S87" s="10" t="n">
-        <v>7.78</v>
+        <v>10.72</v>
       </c>
       <c r="T87" s="3" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v/>
       </c>
       <c r="S90" s="10" t="n">
-        <v>3.45</v>
+        <v>4.91</v>
       </c>
       <c r="T90" s="3" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v/>
       </c>
       <c r="S93" s="10" t="n">
-        <v>1.99</v>
+        <v>3.17</v>
       </c>
       <c r="T93" s="3" t="inlineStr">
         <is>

--- a/docs/ophir/ophir-maliyet-talebi.xlsx
+++ b/docs/ophir/ophir-maliyet-talebi.xlsx
@@ -725,7 +725,7 @@
         <v/>
       </c>
       <c r="S2" s="10" t="n">
-        <v>5.13</v>
+        <v>8.67</v>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="S3" s="10" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v/>
       </c>
       <c r="S4" s="10" t="n">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v/>
       </c>
       <c r="S5" s="10" t="n">
-        <v>3.96</v>
+        <v>4.79</v>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v/>
       </c>
       <c r="S6" s="10" t="n">
-        <v>3.96</v>
+        <v>4.79</v>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="S7" s="10" t="n">
-        <v>3.96</v>
+        <v>4.79</v>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v/>
       </c>
       <c r="S8" s="10" t="n">
-        <v>5.93</v>
+        <v>7.18</v>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v/>
       </c>
       <c r="S9" s="10" t="n">
-        <v>5.93</v>
+        <v>7.18</v>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v/>
       </c>
       <c r="S10" s="10" t="n">
-        <v>6.92</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v/>
       </c>
       <c r="S11" s="10" t="n">
-        <v>3.06</v>
+        <v>3.71</v>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v/>
       </c>
       <c r="S12" s="10" t="n">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v/>
       </c>
       <c r="S13" s="10" t="n">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="S14" s="10" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v/>
       </c>
       <c r="S15" s="10" t="n">
-        <v>1.55</v>
+        <v>2.09</v>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v/>
       </c>
       <c r="S16" s="10" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="S17" s="10" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v/>
       </c>
       <c r="S18" s="10" t="n">
-        <v>1.7</v>
+        <v>2.27</v>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v/>
       </c>
       <c r="S19" s="10" t="n">
-        <v>9.59</v>
+        <v>11.6</v>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v/>
       </c>
       <c r="S20" s="10" t="n">
-        <v>3.96</v>
+        <v>4.79</v>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="S21" s="10" t="n">
-        <v>2.57</v>
+        <v>3.11</v>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v/>
       </c>
       <c r="S22" s="10" t="n">
-        <v>3.8</v>
+        <v>4.59</v>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v/>
       </c>
       <c r="S23" s="10" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v/>
       </c>
       <c r="S24" s="10" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v/>
       </c>
       <c r="S25" s="10" t="n">
-        <v>7.07</v>
+        <v>10.17</v>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v/>
       </c>
       <c r="S26" s="10" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v/>
       </c>
       <c r="S27" s="10" t="n">
-        <v>4.4</v>
+        <v>5.32</v>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v/>
       </c>
       <c r="S28" s="10" t="n">
-        <v>2.54</v>
+        <v>4.34</v>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v/>
       </c>
       <c r="S29" s="10" t="n">
-        <v>9.25</v>
+        <v>11.19</v>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v/>
       </c>
       <c r="S30" s="10" t="n">
-        <v>2.77</v>
+        <v>3.35</v>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v/>
       </c>
       <c r="S31" s="10" t="n">
-        <v>6.28</v>
+        <v>7.6</v>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v/>
       </c>
       <c r="S32" s="10" t="n">
-        <v>6.13</v>
+        <v>7.42</v>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v/>
       </c>
       <c r="S33" s="10" t="n">
-        <v>2.94</v>
+        <v>4.96</v>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v/>
       </c>
       <c r="S34" s="10" t="n">
-        <v>4.86</v>
+        <v>6.94</v>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v/>
       </c>
       <c r="S35" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="S36" s="10" t="n">
-        <v>5.59</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v/>
       </c>
       <c r="S37" s="10" t="n">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v/>
       </c>
       <c r="S38" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v/>
       </c>
       <c r="S39" s="10" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v/>
       </c>
       <c r="S40" s="10" t="n">
-        <v>3.71</v>
+        <v>5.38</v>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v/>
       </c>
       <c r="S41" s="10" t="n">
-        <v>9.69</v>
+        <v>11.72</v>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v/>
       </c>
       <c r="S42" s="10" t="n">
-        <v>2.77</v>
+        <v>3.35</v>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="S43" s="10" t="n">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v/>
       </c>
       <c r="S44" s="10" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="S45" s="10" t="n">
-        <v>2.85</v>
+        <v>4.07</v>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v/>
       </c>
       <c r="S46" s="10" t="n">
-        <v>2.87</v>
+        <v>3.47</v>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v/>
       </c>
       <c r="S47" s="10" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v/>
       </c>
       <c r="S48" s="10" t="n">
-        <v>3.26</v>
+        <v>3.95</v>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v/>
       </c>
       <c r="S49" s="10" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="S50" s="10" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v/>
       </c>
       <c r="S51" s="10" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v/>
       </c>
       <c r="S52" s="10" t="n">
-        <v>3.73</v>
+        <v>5.68</v>
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v/>
       </c>
       <c r="S53" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v/>
       </c>
       <c r="S54" s="10" t="n">
-        <v>3.58</v>
+        <v>5.26</v>
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v/>
       </c>
       <c r="S55" s="10" t="n">
-        <v>4.38</v>
+        <v>6.28</v>
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v/>
       </c>
       <c r="S56" s="10" t="n">
-        <v>4.02</v>
+        <v>6.31</v>
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v/>
       </c>
       <c r="S57" s="10" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v/>
       </c>
       <c r="S58" s="10" t="n">
-        <v>3.06</v>
+        <v>3.71</v>
       </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v/>
       </c>
       <c r="S59" s="10" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v/>
       </c>
       <c r="S60" s="10" t="n">
-        <v>5.45</v>
+        <v>7.78</v>
       </c>
       <c r="T60" s="3" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v/>
       </c>
       <c r="S61" s="10" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="T61" s="3" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v/>
       </c>
       <c r="S62" s="10" t="n">
-        <v>1.83</v>
+        <v>2.39</v>
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v/>
       </c>
       <c r="S63" s="10" t="n">
-        <v>5.03</v>
+        <v>7.18</v>
       </c>
       <c r="T63" s="3" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v/>
       </c>
       <c r="S64" s="10" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="T64" s="3" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v/>
       </c>
       <c r="S65" s="10" t="n">
-        <v>2.34</v>
+        <v>3.95</v>
       </c>
       <c r="T65" s="3" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v/>
       </c>
       <c r="S66" s="10" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="T66" s="3" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v/>
       </c>
       <c r="S67" s="10" t="n">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="T67" s="3" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v/>
       </c>
       <c r="S68" s="10" t="n">
-        <v>2.72</v>
+        <v>4.19</v>
       </c>
       <c r="T68" s="3" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v/>
       </c>
       <c r="S69" s="10" t="n">
-        <v>5.74</v>
+        <v>6.94</v>
       </c>
       <c r="T69" s="3" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v/>
       </c>
       <c r="S70" s="10" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="T70" s="3" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v/>
       </c>
       <c r="S71" s="10" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="T71" s="3" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v/>
       </c>
       <c r="S72" s="10" t="n">
-        <v>2.54</v>
+        <v>4.31</v>
       </c>
       <c r="T72" s="3" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v/>
       </c>
       <c r="S73" s="10" t="n">
-        <v>2.04</v>
+        <v>3.29</v>
       </c>
       <c r="T73" s="3" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v/>
       </c>
       <c r="S74" s="10" t="n">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="T74" s="3" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v/>
       </c>
       <c r="S75" s="10" t="n">
-        <v>9.4</v>
+        <v>11.37</v>
       </c>
       <c r="T75" s="3" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v/>
       </c>
       <c r="S76" s="10" t="n">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="T76" s="3" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v/>
       </c>
       <c r="S77" s="10" t="n">
-        <v>5.19</v>
+        <v>7.42</v>
       </c>
       <c r="T77" s="3" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v/>
       </c>
       <c r="S78" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T78" s="3" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v/>
       </c>
       <c r="S79" s="10" t="n">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="T79" s="3" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v/>
       </c>
       <c r="S80" s="10" t="n">
-        <v>4.2</v>
+        <v>7.54</v>
       </c>
       <c r="T80" s="3" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v/>
       </c>
       <c r="S81" s="10" t="n">
-        <v>5.93</v>
+        <v>7.18</v>
       </c>
       <c r="T81" s="3" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v/>
       </c>
       <c r="S82" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T82" s="3" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v/>
       </c>
       <c r="S83" s="10" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="T83" s="3" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v/>
       </c>
       <c r="S84" s="10" t="n">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="T84" s="3" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v/>
       </c>
       <c r="S85" s="10" t="n">
-        <v>2.72</v>
+        <v>4.19</v>
       </c>
       <c r="T85" s="3" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v/>
       </c>
       <c r="S86" s="10" t="n">
-        <v>4.62</v>
+        <v>6.7</v>
       </c>
       <c r="T86" s="3" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v/>
       </c>
       <c r="S87" s="10" t="n">
-        <v>5.07</v>
+        <v>10.72</v>
       </c>
       <c r="T87" s="3" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v/>
       </c>
       <c r="S88" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T88" s="3" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v/>
       </c>
       <c r="S89" s="10" t="n">
-        <v>6.43</v>
+        <v>7.78</v>
       </c>
       <c r="T89" s="3" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v/>
       </c>
       <c r="S90" s="10" t="n">
-        <v>2.91</v>
+        <v>4.91</v>
       </c>
       <c r="T90" s="3" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v/>
       </c>
       <c r="S91" s="10" t="n">
-        <v>1.48</v>
+        <v>4.31</v>
       </c>
       <c r="T91" s="3" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v/>
       </c>
       <c r="S92" s="10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="T92" s="3" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v/>
       </c>
       <c r="S93" s="10" t="n">
-        <v>2.22</v>
+        <v>3.17</v>
       </c>
       <c r="T93" s="3" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v/>
       </c>
       <c r="S94" s="10" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="T94" s="3" t="inlineStr">
         <is>
